--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/PENNSYLVANIA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/PENNSYLVANIA_2011.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C68">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C343">
